--- a/public/templates/tamplate_ecogreen.xlsx
+++ b/public/templates/tamplate_ecogreen.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\e-OutSourcing\E-outsourcing-trpl210\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{86C58FE0-0631-49F2-8FB1-718CAC96679E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E86B20CF-A5B4-4F9A-BF66-EFFC4488BE5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{2642DFAA-6D1B-4163-AE26-76F379990A6D}"/>
   </bookViews>
@@ -39,25 +39,25 @@
     <t>nomor_tlp</t>
   </si>
   <si>
-    <t>role</t>
-  </si>
-  <si>
     <t>password</t>
   </si>
   <si>
     <t>peraturan :</t>
   </si>
   <si>
-    <t>buatlah data karyawan mengikuti tamplate yang disediakan</t>
-  </si>
-  <si>
     <t>isi kolom harus sesuai dengan baris header</t>
   </si>
   <si>
-    <t>tamplate tabel boleh dipajangkan kebawah tetapi tidak boleh buat tabel baru</t>
-  </si>
-  <si>
     <t>diperbolehkan memanjangkan kolom tetapi tidak boleh memindahkan tabel</t>
+  </si>
+  <si>
+    <t>departemen :</t>
+  </si>
+  <si>
+    <t>( tulis disini )</t>
+  </si>
+  <si>
+    <t>buatlah data mengikuti tamplate yang disediakan, hanya isi departemen di B7 jika mengisi pengguna kepala departemen</t>
   </si>
 </sst>
 </file>
@@ -81,7 +81,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -100,8 +100,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -125,79 +131,8 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
       <top/>
       <bottom style="thin">
         <color indexed="64"/>
@@ -208,47 +143,26 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -563,116 +477,134 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B56FF216-2F7A-4373-96C8-89DD85E9D1DD}">
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.85546875" customWidth="1"/>
-    <col min="2" max="2" width="11.28515625" customWidth="1"/>
+    <col min="2" max="2" width="15.140625" customWidth="1"/>
     <col min="3" max="3" width="14.7109375" customWidth="1"/>
     <col min="4" max="4" width="11.42578125" customWidth="1"/>
     <col min="5" max="5" width="17.85546875" customWidth="1"/>
     <col min="11" max="11" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
-        <v>7</v>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
+        <v>10</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
-      <c r="E2" s="7"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+    </row>
+    <row r="6" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A6" s="7"/>
+      <c r="B6" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="9"/>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="10"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
+      <c r="B7" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="10"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="12"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="12"/>
-      <c r="E5" s="13"/>
-    </row>
-    <row r="7" spans="1:5" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B7" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B8" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D8" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
+      <c r="E8" s="5"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A1:E1"/>
+  <mergeCells count="7">
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="D11:E11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
